--- a/InputData/indst/CtIEPpUESoS/Cost to Impl Eff Policy per Unit E Saved or Shifted.xlsx
+++ b/InputData/indst/CtIEPpUESoS/Cost to Impl Eff Policy per Unit E Saved or Shifted.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jeff Rissman\CodeRepositories\eps-us\InputData\indst\CtIEPpUESoS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndiaEPS/Shared Documents/Completed EPS Variables/indst/indst/CtIEPpUESoS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D712F579-FDFF-4D31-9988-B54209EAC155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{CF7C685B-61BD-4F1A-ADF7-4A836B777C3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47924627-A92D-41DC-B60C-1403275DFA5D}"/>
   <bookViews>
-    <workbookView xWindow="21945" yWindow="3135" windowWidth="34365" windowHeight="18975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="1080" windowWidth="14610" windowHeight="15585" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,14 @@
     <sheet name="shift to electricity" sheetId="8" r:id="rId5"/>
     <sheet name="shift to hydrogen" sheetId="5" r:id="rId6"/>
     <sheet name="substitute fuels for coal" sheetId="9" r:id="rId7"/>
-    <sheet name="CtIEPpUESoS" sheetId="3" r:id="rId8"/>
+    <sheet name="India cost adjustment" sheetId="11" r:id="rId8"/>
+    <sheet name="CtIEPpUESoS" sheetId="3" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -32,6 +36,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -82,26 +87,164 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="183">
+  <si>
+    <t>CtIEPpUESoS Cost to Implement Efficiency Policy per Unit Energy Saved or Shifted</t>
+  </si>
   <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>early retirement of equipment</t>
+  </si>
+  <si>
+    <t>substitute other fuels for coal: conversion costs per unit capacity</t>
+  </si>
+  <si>
+    <t>Alex MacCurdy et al.</t>
+  </si>
+  <si>
+    <t>Babcock and Wilcox</t>
+  </si>
+  <si>
+    <t>Dual Baselines for Industrial Retrofits that Trigger Energy Codes</t>
+  </si>
+  <si>
+    <t>Natural Gas Conversions of Existing Coal-Fired Boilers</t>
+  </si>
+  <si>
+    <t>http://aceee.org/files/proceedings/2013/data/papers/3_166.pdf</t>
+  </si>
+  <si>
+    <t>http://www.babcock.com/library/Documents/MS-14.pdf</t>
+  </si>
+  <si>
+    <t>Page 3-8, Table 4</t>
+  </si>
+  <si>
+    <t>Page 2, "Financial Considerations," paragraph 1</t>
+  </si>
+  <si>
+    <t>cogeneration and WHR: total cost</t>
+  </si>
+  <si>
+    <t>Rocky Mountain Institute</t>
+  </si>
+  <si>
+    <t>McKinsey</t>
+  </si>
+  <si>
+    <t>Reinventing Fire: Bold Business Solutions for the New Energy Era</t>
+  </si>
+  <si>
+    <t>Unlocking Energy Efficiency in the U.S. Economy</t>
+  </si>
+  <si>
+    <t>http://www.rmi.org/RFGraph-Cumulative_2010_value_capital_investment_fuel_savings</t>
+  </si>
+  <si>
+    <t>https://www.sallan.org/pdf-docs/MCKINSEY_US_energy_efficiency.pdf</t>
+  </si>
+  <si>
+    <t>Cumulative 2010 present value of capital investment and fuel savings</t>
+  </si>
+  <si>
+    <t>Tables 15 and 16</t>
+  </si>
+  <si>
+    <t>cogeneration and WHR: annual energy savings</t>
+  </si>
+  <si>
+    <t>Reinventing Fire</t>
+  </si>
+  <si>
+    <t>http://www.rmi.org/RFGraph-US_industry_energy_saving_potential</t>
+  </si>
+  <si>
+    <t>Book page 127, Figure 4-2 (or see link above)</t>
+  </si>
+  <si>
+    <t>elec and hydrogen shifting (boiler conversion)</t>
+  </si>
+  <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>"Achieving Carbon Neutrality in California (Revised Report): 2045 Abatement Cost Estimates"</t>
+  </si>
+  <si>
+    <t>https://ww2.arb.ca.gov/sites/default/files/2020-09/e3_cn_draft_report_supp_data_aug2020.xlsx</t>
+  </si>
+  <si>
+    <t>elec shifting (heat pump)</t>
+  </si>
+  <si>
+    <t>Emerson</t>
+  </si>
+  <si>
+    <t>Industrial Heat Pumps</t>
+  </si>
+  <si>
+    <t>https://climate.emerson.com/documents/vilter-heat-pump-white-paper-en-us-5411194.pdf</t>
+  </si>
+  <si>
+    <t>Notes:</t>
+  </si>
+  <si>
+    <t>This variable supports time series data for adaptation to other regions, but as of EPS 1.5.0, we</t>
+  </si>
+  <si>
+    <t>have only time-invariant data for the U.S.</t>
+  </si>
+  <si>
+    <t>For fuel type shifting we take an average of electric boiler conversion and hydrogen boiler conversion.</t>
+  </si>
+  <si>
+    <t>We assume the majority of energy and costs will be from boiler conversion instead of process heaters.</t>
+  </si>
+  <si>
+    <t>All costs are per BTU of energy saved or shifted per year.  That is, it is the cost to buy equipment that</t>
+  </si>
+  <si>
+    <t>achieves this energy savings/shifting annually.</t>
+  </si>
+  <si>
+    <t>We assume the "proper installation and use of equipment" has no investment cost, as it is a different</t>
+  </si>
+  <si>
+    <t>way of doing things that are already done, rather than doing or buying something new.</t>
+  </si>
+  <si>
+    <t>We do not model costs of R&amp;D per unit of energy saved/shifted as a result of that R&amp;D investment.</t>
+  </si>
+  <si>
+    <t>Currency Year</t>
+  </si>
+  <si>
+    <t>MacCurdy et al. do not specify the year of the currency in Table 4.  We assume it to be the year of the</t>
+  </si>
+  <si>
+    <t xml:space="preserve">publication, which is 2013.  RMI currency is in 2010 dollars.  </t>
+  </si>
+  <si>
+    <t>Babcock and Wilcox do not specify the year of their dollar figures, so we assume it is the year of publication (2010).</t>
+  </si>
+  <si>
+    <t>We adjust the dollars to 2012 dollars using the following conversion factors:</t>
+  </si>
+  <si>
+    <t>2013 to 2012, MacCurdy et al.</t>
+  </si>
+  <si>
+    <t>2010 to 2012, RMI and Babcock and Wilcox</t>
+  </si>
+  <si>
+    <t>See "cpi.xlsx" in the InputData folder for source information.</t>
+  </si>
+  <si>
     <t>Early Retirement of Equipment</t>
   </si>
   <si>
-    <t>Alex MacCurdy et al.</t>
-  </si>
-  <si>
-    <t>Dual Baselines for Industrial Retrofits that Trigger Energy Codes</t>
-  </si>
-  <si>
-    <t>http://aceee.org/files/proceedings/2013/data/papers/3_166.pdf</t>
-  </si>
-  <si>
-    <t>Page 3-8, Table 4</t>
-  </si>
-  <si>
     <t>Methodology Notes:</t>
   </si>
   <si>
@@ -156,21 +299,42 @@
     <t>Investment per Unit Annual Energy Savings ($/BTU)</t>
   </si>
   <si>
-    <t>Rocky Mountain Institute</t>
-  </si>
-  <si>
-    <t>Reinventing Fire: Bold Business Solutions for the New Energy Era</t>
-  </si>
-  <si>
-    <t>http://www.rmi.org/RFGraph-Cumulative_2010_value_capital_investment_fuel_savings</t>
-  </si>
-  <si>
-    <t>Cumulative 2010 present value of capital investment and fuel savings</t>
+    <t>Cogeneration and Waste Heat Recovery, Equipment Efficiency Standards</t>
+  </si>
+  <si>
+    <t>Annual energy savings achievable in 2050 (BTU)</t>
+  </si>
+  <si>
+    <t>CHP &amp; waste heat</t>
+  </si>
+  <si>
+    <t>Total investment cost to achieve those annual savings in 2050</t>
+  </si>
+  <si>
+    <t>The graph used appears below.  To correspond to the total energy savings found above, we want to use the set of pink bars that</t>
+  </si>
+  <si>
+    <t>correspond to investment over the 2010-2050 period.  We assume the key inside the rightmost blue bar applies to all bars, so</t>
+  </si>
+  <si>
+    <t>light pink corresponds to CHP Waste Heat and midtone pink corresponds to efficiency technology.</t>
+  </si>
+  <si>
+    <t>Since RMI only provides a numerical value for the hight of the complete pink bar, not values for each of the three shades of</t>
+  </si>
+  <si>
+    <t>pink that compose it, we muse use pixel-based measurement to obtain our data from the graph.</t>
   </si>
   <si>
     <t>Note on pixel measurement of this bar graph:</t>
   </si>
   <si>
+    <t>RMI's graph was made in Excel.  For this type of graph (namely, white lines separating stacked bars),</t>
+  </si>
+  <si>
+    <t>Excel replaces an equal number of rows of colored pixels</t>
+  </si>
+  <si>
     <t>with white pixels from the upper and lower bar segments at each junction, with an extra row of the bottom bar at each junction replaced if there</t>
   </si>
   <si>
@@ -189,7 +353,247 @@
     <t>Cumulative Cost of Upgrades (2009 $)</t>
   </si>
   <si>
-    <t>CtIEPpUESoS Cost to Implement Efficiency Policy per Unit Energy Saved or Shifted</t>
+    <t>2010-2050, total (pixels)</t>
+  </si>
+  <si>
+    <t>2010-2050, this policy (pixels)</t>
+  </si>
+  <si>
+    <t>Investment, total (2009 $)</t>
+  </si>
+  <si>
+    <t>Investment, this policy (2009 $)</t>
+  </si>
+  <si>
+    <t>Cost per Unit Energy Saved Annually ($/BTU)</t>
+  </si>
+  <si>
+    <t>Tbtu/year</t>
+  </si>
+  <si>
+    <t>2009 to 2012 USD</t>
+  </si>
+  <si>
+    <t>We assume outlays are uniform in each year and that savings also accrue uniformly.</t>
+  </si>
+  <si>
+    <t>McKinsey used a 7 percent discount rate in their main scenario</t>
+  </si>
+  <si>
+    <t>Example 1: Industrial Heat Pump</t>
+  </si>
+  <si>
+    <t>Emerson Industrial heat pump case studies:</t>
+  </si>
+  <si>
+    <t>Annual heat delivered (MMbtu)</t>
+  </si>
+  <si>
+    <t>Capital Cost (USD)</t>
+  </si>
+  <si>
+    <t>$/annual BTU</t>
+  </si>
+  <si>
+    <t>Case Study 1</t>
+  </si>
+  <si>
+    <t>Case Study 2</t>
+  </si>
+  <si>
+    <t>Case Study 3</t>
+  </si>
+  <si>
+    <t>Simple average</t>
+  </si>
+  <si>
+    <t>This is the cost per unit heat delivered via heat pump.</t>
+  </si>
+  <si>
+    <t>We want the cost per unit energy saved or shifted.</t>
+  </si>
+  <si>
+    <t>Therefore, we need to take into account the difference in efficiency of heat use.</t>
+  </si>
+  <si>
+    <t>From variable indst/PIFURfE</t>
+  </si>
+  <si>
+    <t>Percent reduction in fuel use from switching from fossil fuels to heat pump is:</t>
+  </si>
+  <si>
+    <t>Therefore, the capital cost per unit energy saved (not per unit energy delivered) is:</t>
+  </si>
+  <si>
+    <t>Example 2: Industrial Electric Boiler</t>
+  </si>
+  <si>
+    <t>Electric Boiler Conversion</t>
+  </si>
+  <si>
+    <t>Industrial Boiler Inputs</t>
+  </si>
+  <si>
+    <t>General Inputs</t>
+  </si>
+  <si>
+    <t>Input Name</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Equipment Lifetime</t>
+  </si>
+  <si>
+    <t>yr</t>
+  </si>
+  <si>
+    <t>Discount Rate</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>Natural Gas Price</t>
+  </si>
+  <si>
+    <t>$/MMBtu</t>
+  </si>
+  <si>
+    <t>Electricity Emissions Intensity</t>
+  </si>
+  <si>
+    <t>kg CO2e/kWh</t>
+  </si>
+  <si>
+    <t>Natural Gas Emissions Intensity</t>
+  </si>
+  <si>
+    <t>kg CO2e/MMBtu</t>
+  </si>
+  <si>
+    <t>Electric Boiler</t>
+  </si>
+  <si>
+    <t>Natural Gas Boiler</t>
+  </si>
+  <si>
+    <t>Boiler Purchase Price</t>
+  </si>
+  <si>
+    <t>$</t>
+  </si>
+  <si>
+    <t>Boiler Efficiency</t>
+  </si>
+  <si>
+    <t>Hourly Service Demand</t>
+  </si>
+  <si>
+    <t>MMBtu/hr</t>
+  </si>
+  <si>
+    <t>Annual Operating Hours</t>
+  </si>
+  <si>
+    <t>hr/yr</t>
+  </si>
+  <si>
+    <t>Annual Service Demand</t>
+  </si>
+  <si>
+    <t>MMBtu/yr</t>
+  </si>
+  <si>
+    <t>Investment per Unit Energy Converted in First Year ($/BTU)</t>
+  </si>
+  <si>
+    <t>$/BTU</t>
+  </si>
+  <si>
+    <t>Hydrogen Boiler Conversion</t>
+  </si>
+  <si>
+    <t>Synthetic Natural Gas Price (Conservative)</t>
+  </si>
+  <si>
+    <t>Synthetic Natural Gas Price (Optimistic)</t>
+  </si>
+  <si>
+    <t>Hydrogen Price (Conservative)</t>
+  </si>
+  <si>
+    <t>Hydrogen Price (Optimistic)</t>
+  </si>
+  <si>
+    <t>Hydrogen Storage and Delivery Cost</t>
+  </si>
+  <si>
+    <t>$/MMBTU</t>
+  </si>
+  <si>
+    <t>Hydrogen Boiler Conservative</t>
+  </si>
+  <si>
+    <t>Hydrogen Boiler Optimistic</t>
+  </si>
+  <si>
+    <t>Natural Gas Boiler Pice</t>
+  </si>
+  <si>
+    <t>H2 Boiler Price</t>
+  </si>
+  <si>
+    <t>H2 Boiler Efficiency</t>
+  </si>
+  <si>
+    <t>Substitute Other Fuels for Coal</t>
+  </si>
+  <si>
+    <t>We estimate the cost of converting coal equipment to use other fuel types</t>
+  </si>
+  <si>
+    <t>via the conversion of coal-fired biolers to natural gas, because of the</t>
+  </si>
+  <si>
+    <t>availability of data.</t>
+  </si>
+  <si>
+    <t>Typical Pulverized Coal to Natural Gas Conversions</t>
+  </si>
+  <si>
+    <t>Estimate</t>
+  </si>
+  <si>
+    <t>Cost per Unit Capacity ($/kW)</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Avg</t>
+  </si>
+  <si>
+    <t>Industrial Boiler Capacity Factor</t>
+  </si>
+  <si>
+    <t>Hours per Year</t>
+  </si>
+  <si>
+    <t>Investment Cost per Unit Annual Energy Converted ($/kWh)</t>
+  </si>
+  <si>
+    <t>Investment per Unit Energy Converted ($/BTU)</t>
+  </si>
+  <si>
+    <t>Cost ($/BTU)</t>
   </si>
   <si>
     <t>early eqpt retirement</t>
@@ -204,412 +608,34 @@
     <t>eqpt efficiency stds</t>
   </si>
   <si>
+    <t>shift to electricity</t>
+  </si>
+  <si>
+    <t>shift to hydrogen</t>
+  </si>
+  <si>
     <t>research and development</t>
   </si>
   <si>
-    <t>early retirement of equipment</t>
-  </si>
-  <si>
-    <t>Notes:</t>
-  </si>
-  <si>
-    <t>achieves this energy savings/shifting annually.</t>
-  </si>
-  <si>
-    <t>All costs are per BTU of energy saved or shifted per year.  That is, it is the cost to buy equipment that</t>
-  </si>
-  <si>
-    <t>Reinventing Fire</t>
-  </si>
-  <si>
-    <t>http://www.rmi.org/RFGraph-US_industry_energy_saving_potential</t>
-  </si>
-  <si>
-    <t>Book page 127, Figure 4-2 (or see link above)</t>
-  </si>
-  <si>
-    <t>Annual energy savings achievable in 2050 (BTU)</t>
-  </si>
-  <si>
-    <t>Total investment cost to achieve those annual savings in 2050</t>
-  </si>
-  <si>
-    <t>RMI's graph was made in Excel.  For this type of graph (namely, white lines separating stacked bars),</t>
-  </si>
-  <si>
-    <t>Excel replaces an equal number of rows of colored pixels</t>
-  </si>
-  <si>
-    <t>Cost per Unit Energy Saved Annually ($/BTU)</t>
-  </si>
-  <si>
-    <t>The graph used appears below.  To correspond to the total energy savings found above, we want to use the set of pink bars that</t>
-  </si>
-  <si>
-    <t>correspond to investment over the 2010-2050 period.  We assume the key inside the rightmost blue bar applies to all bars, so</t>
-  </si>
-  <si>
-    <t>light pink corresponds to CHP Waste Heat and midtone pink corresponds to efficiency technology.</t>
-  </si>
-  <si>
-    <t>Since RMI only provides a numerical value for the hight of the complete pink bar, not values for each of the three shades of</t>
-  </si>
-  <si>
-    <t>pink that compose it, we muse use pixel-based measurement to obtain our data from the graph.</t>
-  </si>
-  <si>
-    <t>CHP &amp; waste heat</t>
-  </si>
-  <si>
-    <t>2010-2050, this policy (pixels)</t>
-  </si>
-  <si>
-    <t>Investment, total (2009 $)</t>
-  </si>
-  <si>
-    <t>2010-2050, total (pixels)</t>
-  </si>
-  <si>
-    <t>Investment, this policy (2009 $)</t>
-  </si>
-  <si>
-    <t>Cogeneration and Waste Heat Recovery, Equipment Efficiency Standards</t>
-  </si>
-  <si>
-    <t>We assume the "proper installation and use of equipment" has no investment cost, as it is a different</t>
-  </si>
-  <si>
-    <t>way of doing things that are already done, rather than doing or buying something new.</t>
-  </si>
-  <si>
-    <t>Currency Year</t>
-  </si>
-  <si>
-    <t>MacCurdy et al. do not specify the year of the currency in Table 4.  We assume it to be the year of the</t>
-  </si>
-  <si>
-    <t>Babcock and Wilcox do not specify the year of their dollar figures, so we assume it is the year of publication (2010).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">publication, which is 2013.  RMI currency is in 2010 dollars.  </t>
-  </si>
-  <si>
-    <t>See "cpi.xlsx" in the InputData folder for source information.</t>
-  </si>
-  <si>
-    <t>We adjust the dollars to 2012 dollars using the following conversion factors:</t>
-  </si>
-  <si>
-    <t>2013 to 2012, MacCurdy et al.</t>
-  </si>
-  <si>
-    <t>2010 to 2012, RMI and Babcock and Wilcox</t>
-  </si>
-  <si>
-    <t>This variable supports time series data for adaptation to other regions, but as of EPS 1.5.0, we</t>
-  </si>
-  <si>
-    <t>have only time-invariant data for the U.S.</t>
-  </si>
-  <si>
-    <t>Cost ($/BTU)</t>
-  </si>
-  <si>
-    <t>Boiler Purchase Price</t>
-  </si>
-  <si>
-    <t>Electric Boiler</t>
-  </si>
-  <si>
-    <t>Boiler Efficiency</t>
-  </si>
-  <si>
-    <t>Hourly Service Demand</t>
-  </si>
-  <si>
-    <t>Industrial Boiler Inputs</t>
-  </si>
-  <si>
-    <t>Input Name</t>
-  </si>
-  <si>
-    <t>Units</t>
-  </si>
-  <si>
-    <t>$</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>MMBtu/hr</t>
-  </si>
-  <si>
-    <t>Annual Operating Hours</t>
-  </si>
-  <si>
-    <t>hr/yr</t>
-  </si>
-  <si>
-    <t>Annual Service Demand</t>
-  </si>
-  <si>
-    <t>MMBtu/yr</t>
-  </si>
-  <si>
-    <t>E3</t>
-  </si>
-  <si>
-    <t>"Achieving Carbon Neutrality in California (Revised Report): 2045 Abatement Cost Estimates"</t>
-  </si>
-  <si>
-    <t>https://ww2.arb.ca.gov/sites/default/files/2020-09/e3_cn_draft_report_supp_data_aug2020.xlsx</t>
-  </si>
-  <si>
-    <t>Electric Boiler Conversion</t>
-  </si>
-  <si>
-    <t>Hydrogen Boiler Conversion</t>
-  </si>
-  <si>
-    <t>General Inputs</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Equipment Lifetime</t>
-  </si>
-  <si>
-    <t>yr</t>
-  </si>
-  <si>
-    <t>Discount Rate</t>
-  </si>
-  <si>
-    <t>Natural Gas Price</t>
-  </si>
-  <si>
-    <t>$/MMBtu</t>
-  </si>
-  <si>
-    <t>Synthetic Natural Gas Price (Conservative)</t>
-  </si>
-  <si>
-    <t>Synthetic Natural Gas Price (Optimistic)</t>
-  </si>
-  <si>
-    <t>Hydrogen Price (Conservative)</t>
-  </si>
-  <si>
-    <t>Hydrogen Price (Optimistic)</t>
-  </si>
-  <si>
-    <t>Hydrogen Storage and Delivery Cost</t>
-  </si>
-  <si>
-    <t>$/MMBTU</t>
-  </si>
-  <si>
-    <t>Hydrogen Boiler Conservative</t>
-  </si>
-  <si>
-    <t>Hydrogen Boiler Optimistic</t>
-  </si>
-  <si>
-    <t>Natural Gas Boiler Pice</t>
-  </si>
-  <si>
-    <t>H2 Boiler Price</t>
-  </si>
-  <si>
-    <t>H2 Boiler Efficiency</t>
-  </si>
-  <si>
-    <t>Electricity Emissions Intensity</t>
-  </si>
-  <si>
-    <t>kg CO2e/kWh</t>
-  </si>
-  <si>
-    <t>Natural Gas Emissions Intensity</t>
-  </si>
-  <si>
-    <t>kg CO2e/MMBtu</t>
-  </si>
-  <si>
-    <t>Natural Gas Boiler</t>
-  </si>
-  <si>
-    <t>Investment per Unit Energy Converted in First Year ($/BTU)</t>
-  </si>
-  <si>
-    <t>For fuel type shifting we take an average of electric boiler conversion and hydrogen boiler conversion.</t>
-  </si>
-  <si>
-    <t>We assume the majority of energy and costs will be from boiler conversion instead of process heaters.</t>
-  </si>
-  <si>
-    <t>Emerson Industrial heat pump case studies:</t>
-  </si>
-  <si>
-    <t>Case Study 1</t>
-  </si>
-  <si>
-    <t>Annual heat delivered (MMbtu)</t>
-  </si>
-  <si>
-    <t>Capital Cost (USD)</t>
-  </si>
-  <si>
-    <t>Case Study 2</t>
-  </si>
-  <si>
-    <t>Case Study 3</t>
-  </si>
-  <si>
-    <t>$/annual BTU</t>
-  </si>
-  <si>
-    <t>Simple average</t>
-  </si>
-  <si>
-    <t>We do not model costs of R&amp;D per unit of energy saved/shifted as a result of that R&amp;D investment.</t>
-  </si>
-  <si>
-    <t>Emerson</t>
-  </si>
-  <si>
-    <t>Industrial Heat Pumps</t>
-  </si>
-  <si>
-    <t>https://climate.emerson.com/documents/vilter-heat-pump-white-paper-en-us-5411194.pdf</t>
-  </si>
-  <si>
-    <t>This is the cost per unit heat delivered via heat pump.</t>
-  </si>
-  <si>
-    <t>We want the cost per unit energy saved or shifted.</t>
-  </si>
-  <si>
-    <t>Therefore, we need to take into account the difference in efficiency of heat use.</t>
-  </si>
-  <si>
-    <t>From variable indst/PIFURfE</t>
-  </si>
-  <si>
-    <t>Percent reduction in fuel use from switching from fossil fuels to heat pump is:</t>
-  </si>
-  <si>
-    <t>Therefore, the capital cost per unit energy saved (not per unit energy delivered) is:</t>
-  </si>
-  <si>
-    <t>Substitute Other Fuels for Coal</t>
-  </si>
-  <si>
-    <t>We estimate the cost of converting coal equipment to use other fuel types</t>
-  </si>
-  <si>
-    <t>via the conversion of coal-fired biolers to natural gas, because of the</t>
-  </si>
-  <si>
-    <t>availability of data.</t>
-  </si>
-  <si>
-    <t>Typical Pulverized Coal to Natural Gas Conversions</t>
-  </si>
-  <si>
-    <t>Estimate</t>
-  </si>
-  <si>
-    <t>Cost per Unit Capacity ($/kW)</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>High</t>
-  </si>
-  <si>
-    <t>Avg</t>
-  </si>
-  <si>
-    <t>Industrial Boiler Capacity Factor</t>
-  </si>
-  <si>
-    <t>Hours per Year</t>
-  </si>
-  <si>
-    <t>Investment Cost per Unit Annual Energy Converted ($/kWh)</t>
-  </si>
-  <si>
-    <t>Investment per Unit Energy Converted ($/BTU)</t>
-  </si>
-  <si>
-    <t>substitute other fuels for coal: conversion costs per unit capacity</t>
-  </si>
-  <si>
-    <t>Babcock and Wilcox</t>
-  </si>
-  <si>
-    <t>Natural Gas Conversions of Existing Coal-Fired Boilers</t>
-  </si>
-  <si>
-    <t>http://www.babcock.com/library/Documents/MS-14.pdf</t>
-  </si>
-  <si>
-    <t>Page 2, "Financial Considerations," paragraph 1</t>
-  </si>
-  <si>
-    <t>Tbtu/year</t>
-  </si>
-  <si>
-    <t>We assume outlays are uniform in each year and that savings also accrue uniformly.</t>
-  </si>
-  <si>
-    <t>McKinsey used a 7 percent discount rate in their main scenario</t>
-  </si>
-  <si>
-    <t>2009 to 2012 USD</t>
-  </si>
-  <si>
-    <t>cogeneration and WHR: total cost</t>
-  </si>
-  <si>
-    <t>cogeneration and WHR: annual energy savings</t>
-  </si>
-  <si>
-    <t>McKinsey</t>
-  </si>
-  <si>
-    <t>Unlocking Energy Efficiency in the U.S. Economy</t>
-  </si>
-  <si>
-    <t>https://www.sallan.org/pdf-docs/MCKINSEY_US_energy_efficiency.pdf</t>
-  </si>
-  <si>
-    <t>Tables 15 and 16</t>
-  </si>
-  <si>
-    <t>shift to electricity</t>
-  </si>
-  <si>
-    <t>shift to hydrogen</t>
-  </si>
-  <si>
-    <t>Example 1: Industrial Heat Pump</t>
-  </si>
-  <si>
-    <t>Example 2: Industrial Electric Boiler</t>
-  </si>
-  <si>
-    <t>$/BTU</t>
-  </si>
-  <si>
-    <t>elec and hydrogen shifting (boiler conversion)</t>
-  </si>
-  <si>
-    <t>elec shifting (heat pump)</t>
+    <t>Share of spending for construction and misc</t>
+  </si>
+  <si>
+    <t>Share of spending for machinery</t>
+  </si>
+  <si>
+    <t>Calculated India multiplier</t>
+  </si>
+  <si>
+    <t>For India, we adjust the US costs. We use the ratio of India:US power plant costs to adjust costs for machinery, and</t>
+  </si>
+  <si>
+    <t>the ratio of GDP per capita to adjust costs for construction and other business sector services.</t>
+  </si>
+  <si>
+    <t>India:US cost adjustment, power plants</t>
+  </si>
+  <si>
+    <t>India:US cost adjustment, GDP per capita</t>
   </si>
 </sst>
 </file>
@@ -851,7 +877,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
@@ -940,15 +966,11 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Body: normal cell" xfId="6" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1113,6 +1135,55 @@
         <a:xfrm>
           <a:off x="4076700" y="1962150"/>
           <a:ext cx="4085714" cy="4238095"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>69850</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>131287</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BA9E1751-E762-47E8-81DF-B4E3D50BA8E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1181100" y="0"/>
+          <a:ext cx="8642350" cy="3261837"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1411,7 +1482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="81.7109375" customWidth="1"/>
@@ -1420,26 +1491,26 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>154</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1452,42 +1523,42 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6" t="s">
-        <v>156</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>157</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>158</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
-        <v>163</v>
+        <v>12</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>154</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>165</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1500,36 +1571,36 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>166</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B14" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>167</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D15" t="s">
-        <v>168</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="8" t="s">
-        <v>164</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
@@ -1539,32 +1610,32 @@
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="8" t="s">
-        <v>174</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>91</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1574,17 +1645,17 @@
     </row>
     <row r="28" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="3" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" s="8" t="s">
-        <v>175</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>131</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.25">
@@ -1594,87 +1665,87 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
-        <v>132</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B34" s="3" t="s">
-        <v>133</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>121</v>
+        <v>37</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>130</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>67</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -1682,7 +1753,7 @@
         <v>0.98699999999999999</v>
       </c>
       <c r="B57" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -1690,12 +1761,42 @@
         <v>1.0549999999999999</v>
       </c>
       <c r="B58" t="s">
-        <v>73</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>70</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>0.50596615326007399</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>3.878298458735905E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1724,62 +1825,62 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>9</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>10</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>13</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="B11" s="5">
         <v>4262</v>
@@ -1794,7 +1895,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="B12" s="5">
         <v>8738</v>
@@ -1809,7 +1910,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="B13" s="5">
         <v>13901</v>
@@ -1824,7 +1925,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -1835,7 +1936,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="B16" s="10"/>
     </row>
@@ -1847,7 +1948,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="B19" s="8"/>
     </row>
@@ -1882,7 +1983,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1890,13 +1991,13 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="B3" s="10"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="B4" s="18">
         <f>2.4*10^15</f>
@@ -1911,77 +2012,77 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -1990,21 +2091,21 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E24" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="B25" s="5">
         <v>114</v>
@@ -2035,7 +2136,7 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="B28" s="20"/>
       <c r="C28" s="15"/>
@@ -2043,7 +2144,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="B29" s="19">
         <f>E25/B4</f>
@@ -2175,7 +2276,7 @@
         <v>201.66666666666666</v>
       </c>
       <c r="C4" t="s">
-        <v>159</v>
+        <v>93</v>
       </c>
       <c r="M4">
         <f>1550+870</f>
@@ -2188,7 +2289,7 @@
         <v>5.2772702980209352E-5</v>
       </c>
       <c r="O5" t="s">
-        <v>162</v>
+        <v>94</v>
       </c>
       <c r="Q5">
         <v>1.07</v>
@@ -2196,12 +2297,12 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>160</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>161</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2222,35 +2323,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
-        <v>171</v>
-      </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-    </row>
-    <row r="2" spans="1:4" s="47" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="46"/>
+      <c r="A1" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="B5" s="35" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="B6">
         <v>56603</v>
@@ -2265,7 +2366,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="B7">
         <v>25717</v>
@@ -2280,7 +2381,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="B8">
         <v>60507</v>
@@ -2295,7 +2396,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="B9">
         <f>AVERAGE(B6:B8)</f>
@@ -2312,27 +2413,27 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>134</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2342,7 +2443,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2352,45 +2453,45 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="48" t="s">
-        <v>172</v>
-      </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="49"/>
-      <c r="D23" s="49"/>
+      <c r="A23" s="46" t="s">
+        <v>112</v>
+      </c>
+      <c r="B23" s="47"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="22" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="23" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="24" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="C30" s="24">
         <v>25</v>
@@ -2398,10 +2499,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="24" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="C31" s="25">
         <v>0.05</v>
@@ -2409,10 +2510,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="24" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C32" s="26">
         <v>6.5242598122280206</v>
@@ -2421,10 +2522,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="24" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="C33" s="32">
         <v>6.3954140084752677E-3</v>
@@ -2432,10 +2533,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="24" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="C34" s="32">
         <v>52.826854199999993</v>
@@ -2443,29 +2544,29 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="23" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="24" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="C38" s="27">
         <v>53860</v>
@@ -2476,10 +2577,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="24" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="C39" s="25">
         <v>1</v>
@@ -2490,10 +2591,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="24" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="C40" s="29">
         <v>3.3475000000000001</v>
@@ -2504,10 +2605,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="24" t="s">
-        <v>87</v>
+        <v>136</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>88</v>
+        <v>137</v>
       </c>
       <c r="C41" s="30">
         <v>5280</v>
@@ -2518,10 +2619,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="24" t="s">
-        <v>89</v>
+        <v>138</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="C42" s="30">
         <f>C40*C41</f>
@@ -2537,23 +2638,23 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="B45" s="8"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="51">
+      <c r="A46" s="36">
         <f>C38/(C42*10^6)</f>
         <v>3.047276348247222E-6</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="48" t="s">
-        <v>21</v>
-      </c>
-      <c r="B51" s="49"/>
-      <c r="C51" s="49"/>
-      <c r="D51" s="49"/>
+      <c r="A51" s="46" t="s">
+        <v>67</v>
+      </c>
+      <c r="B51" s="47"/>
+      <c r="C51" s="47"/>
+      <c r="D51" s="47"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="36">
@@ -2561,7 +2662,7 @@
         <v>4.604988339008401E-6</v>
       </c>
       <c r="B53" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -2585,7 +2686,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2593,26 +2694,26 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="23" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="C5" s="24">
         <v>25</v>
@@ -2620,10 +2721,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="C6" s="25">
         <v>0.05</v>
@@ -2631,10 +2732,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C7" s="26">
         <f>'shift to electricity'!C32</f>
@@ -2643,10 +2744,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C8" s="27">
         <v>44</v>
@@ -2654,10 +2755,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C9" s="27">
         <v>34</v>
@@ -2665,10 +2766,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C10" s="27">
         <v>21</v>
@@ -2676,10 +2777,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C11" s="27">
         <v>15</v>
@@ -2687,10 +2788,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
-        <v>107</v>
+        <v>147</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="C12" s="27">
         <v>4</v>
@@ -2698,29 +2799,29 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="C16" s="27">
         <v>87540</v>
@@ -2731,10 +2832,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="C17" s="27">
         <f>C16*1.5</f>
@@ -2746,10 +2847,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="24" t="s">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="C18" s="25">
         <f>D18</f>
@@ -2761,10 +2862,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
-        <v>80</v>
+        <v>134</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>86</v>
+        <v>135</v>
       </c>
       <c r="C19" s="29">
         <v>3.3475000000000001</v>
@@ -2775,10 +2876,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
-        <v>87</v>
+        <v>136</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>88</v>
+        <v>137</v>
       </c>
       <c r="C20" s="30">
         <v>5280</v>
@@ -2789,10 +2890,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
-        <v>89</v>
+        <v>138</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="C21" s="30">
         <f>C19*C20</f>
@@ -2805,11 +2906,11 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="50">
+      <c r="A24" s="48">
         <f>AVERAGE(C17:D17)/(AVERAGE(C21:D21)*10^6)</f>
         <v>6.1910177201439334E-6</v>
       </c>
@@ -2832,26 +2933,26 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="35"/>
       <c r="B5" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="C5" s="35"/>
     </row>
@@ -2861,23 +2962,23 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="39" t="s">
-        <v>144</v>
+        <v>158</v>
       </c>
       <c r="B7" s="40"/>
       <c r="C7" s="12"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>146</v>
+        <v>160</v>
       </c>
       <c r="C8" s="12"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="B9" s="41">
         <v>50</v>
@@ -2886,7 +2987,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="B10" s="41">
         <v>75</v>
@@ -2895,7 +2996,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="42" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="B11" s="43">
         <f>AVERAGE(B9:B10)</f>
@@ -2904,7 +3005,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B13" s="10"/>
     </row>
@@ -2915,7 +3016,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -2926,7 +3027,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="B19" s="10"/>
     </row>
@@ -2938,7 +3039,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="B22" s="10"/>
     </row>
@@ -2950,7 +3051,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="B25" s="8"/>
     </row>
@@ -2966,816 +3067,1196 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80C2E265-4924-4EE6-97CE-01F06756A9F9}">
+  <dimension ref="A22:B25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="40.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>176</v>
+      </c>
+      <c r="B22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>177</v>
+      </c>
+      <c r="B23">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>178</v>
+      </c>
+      <c r="B25">
+        <f>B22*About!A65+'India cost adjustment'!B23*About!A68</f>
+        <v>0.27237456892371653</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AH8"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.140625" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" customWidth="1"/>
-    <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B1" s="12">
-        <v>2018</v>
-      </c>
-      <c r="C1">
-        <v>2019</v>
-      </c>
-      <c r="D1" s="12">
-        <v>2020</v>
-      </c>
-      <c r="E1">
+        <v>168</v>
+      </c>
+      <c r="B1" s="1">
         <v>2021</v>
       </c>
-      <c r="F1" s="12">
+      <c r="C1" s="33">
         <v>2022</v>
       </c>
-      <c r="G1">
+      <c r="D1" s="1">
         <v>2023</v>
       </c>
-      <c r="H1" s="12">
+      <c r="E1" s="33">
         <v>2024</v>
       </c>
-      <c r="I1">
+      <c r="F1" s="1">
         <v>2025</v>
       </c>
-      <c r="J1" s="12">
+      <c r="G1" s="33">
         <v>2026</v>
       </c>
-      <c r="K1">
+      <c r="H1" s="1">
         <v>2027</v>
       </c>
-      <c r="L1" s="12">
+      <c r="I1" s="33">
         <v>2028</v>
       </c>
-      <c r="M1">
+      <c r="J1" s="1">
         <v>2029</v>
       </c>
-      <c r="N1" s="12">
+      <c r="K1" s="33">
         <v>2030</v>
       </c>
-      <c r="O1">
+      <c r="L1" s="1">
         <v>2031</v>
       </c>
-      <c r="P1" s="12">
+      <c r="M1" s="33">
         <v>2032</v>
       </c>
-      <c r="Q1">
+      <c r="N1" s="1">
         <v>2033</v>
       </c>
-      <c r="R1" s="12">
+      <c r="O1" s="33">
         <v>2034</v>
       </c>
-      <c r="S1">
+      <c r="P1" s="1">
         <v>2035</v>
       </c>
-      <c r="T1" s="12">
+      <c r="Q1" s="33">
         <v>2036</v>
       </c>
-      <c r="U1">
+      <c r="R1" s="1">
         <v>2037</v>
       </c>
-      <c r="V1" s="12">
+      <c r="S1" s="33">
         <v>2038</v>
       </c>
-      <c r="W1">
+      <c r="T1" s="1">
         <v>2039</v>
       </c>
-      <c r="X1" s="12">
+      <c r="U1" s="33">
         <v>2040</v>
       </c>
-      <c r="Y1">
+      <c r="V1" s="1">
         <v>2041</v>
       </c>
-      <c r="Z1" s="12">
+      <c r="W1" s="33">
         <v>2042</v>
       </c>
-      <c r="AA1">
+      <c r="X1" s="1">
         <v>2043</v>
       </c>
-      <c r="AB1" s="12">
+      <c r="Y1" s="33">
         <v>2044</v>
       </c>
-      <c r="AC1">
+      <c r="Z1" s="1">
         <v>2045</v>
       </c>
-      <c r="AD1" s="12">
+      <c r="AA1" s="33">
         <v>2046</v>
       </c>
-      <c r="AE1">
+      <c r="AB1" s="1">
         <v>2047</v>
       </c>
-      <c r="AF1" s="12">
+      <c r="AC1" s="33">
         <v>2048</v>
       </c>
-      <c r="AG1">
+      <c r="AD1" s="1">
         <v>2049</v>
       </c>
-      <c r="AH1" s="12">
+      <c r="AE1" s="33">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AF1" s="33">
+        <v>2051</v>
+      </c>
+      <c r="AG1" s="33">
+        <v>2052</v>
+      </c>
+      <c r="AH1" s="33">
+        <v>2053</v>
+      </c>
+      <c r="AI1" s="33">
+        <v>2054</v>
+      </c>
+      <c r="AJ1" s="33">
+        <v>2055</v>
+      </c>
+      <c r="AK1" s="33">
+        <v>2056</v>
+      </c>
+      <c r="AL1" s="33">
+        <v>2057</v>
+      </c>
+      <c r="AM1" s="33">
+        <v>2058</v>
+      </c>
+      <c r="AN1" s="33">
+        <v>2059</v>
+      </c>
+      <c r="AO1" s="33">
+        <v>2060</v>
+      </c>
+      <c r="AP1" s="33">
+        <v>2061</v>
+      </c>
+      <c r="AQ1" s="33">
+        <v>2062</v>
+      </c>
+      <c r="AR1" s="33">
+        <v>2063</v>
+      </c>
+      <c r="AS1" s="33">
+        <v>2064</v>
+      </c>
+      <c r="AT1" s="33">
+        <v>2065</v>
+      </c>
+      <c r="AU1" s="33">
+        <v>2066</v>
+      </c>
+      <c r="AV1" s="33">
+        <v>2067</v>
+      </c>
+      <c r="AW1" s="33">
+        <v>2068</v>
+      </c>
+      <c r="AX1" s="33">
+        <v>2069</v>
+      </c>
+      <c r="AY1" s="33">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>169</v>
       </c>
       <c r="B2" s="17">
-        <f>'early retirement'!A20*About!$A$57</f>
-        <v>1.4243732995275992E-4</v>
+        <f>'early retirement'!A20*About!$A$57*'India cost adjustment'!$B$25</f>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="C2" s="17">
         <f>$B2</f>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="D2" s="17">
-        <f>$B2</f>
-        <v>1.4243732995275992E-4</v>
+        <f t="shared" ref="D2:AY2" si="0">$B2</f>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="E2" s="17">
-        <f t="shared" ref="E2:AH8" si="0">$B2</f>
-        <v>1.4243732995275992E-4</v>
+        <f t="shared" si="0"/>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="F2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="G2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="H2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="I2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="J2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="K2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="L2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="M2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="N2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="O2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="P2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="Q2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="R2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="S2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="T2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="U2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="V2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="W2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="X2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="Y2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="Z2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="AA2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="AB2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="AC2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="AD2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="AE2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="AF2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="AG2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
+        <v>3.8796306344528161E-5</v>
       </c>
       <c r="AH2" s="17">
         <f t="shared" si="0"/>
-        <v>1.4243732995275992E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.25">
+        <v>3.8796306344528161E-5</v>
+      </c>
+      <c r="AI2" s="17">
+        <f t="shared" si="0"/>
+        <v>3.8796306344528161E-5</v>
+      </c>
+      <c r="AJ2" s="17">
+        <f t="shared" si="0"/>
+        <v>3.8796306344528161E-5</v>
+      </c>
+      <c r="AK2" s="17">
+        <f t="shared" si="0"/>
+        <v>3.8796306344528161E-5</v>
+      </c>
+      <c r="AL2" s="17">
+        <f t="shared" si="0"/>
+        <v>3.8796306344528161E-5</v>
+      </c>
+      <c r="AM2" s="17">
+        <f t="shared" si="0"/>
+        <v>3.8796306344528161E-5</v>
+      </c>
+      <c r="AN2" s="17">
+        <f t="shared" si="0"/>
+        <v>3.8796306344528161E-5</v>
+      </c>
+      <c r="AO2" s="17">
+        <f t="shared" si="0"/>
+        <v>3.8796306344528161E-5</v>
+      </c>
+      <c r="AP2" s="17">
+        <f t="shared" si="0"/>
+        <v>3.8796306344528161E-5</v>
+      </c>
+      <c r="AQ2" s="17">
+        <f t="shared" si="0"/>
+        <v>3.8796306344528161E-5</v>
+      </c>
+      <c r="AR2" s="17">
+        <f t="shared" si="0"/>
+        <v>3.8796306344528161E-5</v>
+      </c>
+      <c r="AS2" s="17">
+        <f t="shared" si="0"/>
+        <v>3.8796306344528161E-5</v>
+      </c>
+      <c r="AT2" s="17">
+        <f t="shared" si="0"/>
+        <v>3.8796306344528161E-5</v>
+      </c>
+      <c r="AU2" s="17">
+        <f t="shared" si="0"/>
+        <v>3.8796306344528161E-5</v>
+      </c>
+      <c r="AV2" s="17">
+        <f t="shared" si="0"/>
+        <v>3.8796306344528161E-5</v>
+      </c>
+      <c r="AW2" s="17">
+        <f t="shared" si="0"/>
+        <v>3.8796306344528161E-5</v>
+      </c>
+      <c r="AX2" s="17">
+        <f t="shared" si="0"/>
+        <v>3.8796306344528161E-5</v>
+      </c>
+      <c r="AY2" s="17">
+        <f t="shared" si="0"/>
+        <v>3.8796306344528161E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>170</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:R8" si="1">$B3</f>
         <v>0</v>
       </c>
       <c r="D3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="F3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="H3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="L3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="M3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="N3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="P3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="Q3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R3">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AG3">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AH3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AO3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>0</v>
+      </c>
+      <c r="AQ3">
+        <v>0</v>
+      </c>
+      <c r="AR3">
+        <v>0</v>
+      </c>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+      <c r="AT3">
+        <v>0</v>
+      </c>
+      <c r="AU3">
+        <v>0</v>
+      </c>
+      <c r="AV3">
+        <v>0</v>
+      </c>
+      <c r="AW3">
+        <v>0</v>
+      </c>
+      <c r="AX3">
+        <v>0</v>
+      </c>
+      <c r="AY3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>171</v>
       </c>
       <c r="B4" s="17">
-        <f>'cogen and WHR'!B29*About!$A$58</f>
-        <v>2.4092251461988303E-5</v>
+        <f>'cogen and WHR'!B29*About!$A$58*'India cost adjustment'!$B$25</f>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="C4" s="17">
-        <f t="shared" si="1"/>
-        <v>2.4092251461988303E-5</v>
+        <f>$B4</f>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="D4" s="17">
-        <f t="shared" si="1"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" ref="D4:AY7" si="1">$B4</f>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="E4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="F4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="G4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="H4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="I4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="J4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="K4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="L4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="M4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="N4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="O4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="P4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="Q4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="R4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="S4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="T4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="U4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="V4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="W4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="X4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="Y4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="Z4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="AA4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="AB4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="AC4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="AD4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="AE4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="AF4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="AG4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
       </c>
       <c r="AH4" s="17">
-        <f t="shared" si="0"/>
-        <v>2.4092251461988303E-5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
+      </c>
+      <c r="AI4" s="17">
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
+      </c>
+      <c r="AJ4" s="17">
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
+      </c>
+      <c r="AK4" s="17">
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
+      </c>
+      <c r="AL4" s="17">
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
+      </c>
+      <c r="AM4" s="17">
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
+      </c>
+      <c r="AN4" s="17">
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
+      </c>
+      <c r="AO4" s="17">
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
+      </c>
+      <c r="AP4" s="17">
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
+      </c>
+      <c r="AQ4" s="17">
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
+      </c>
+      <c r="AR4" s="17">
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
+      </c>
+      <c r="AS4" s="17">
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
+      </c>
+      <c r="AT4" s="17">
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
+      </c>
+      <c r="AU4" s="17">
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
+      </c>
+      <c r="AV4" s="17">
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
+      </c>
+      <c r="AW4" s="17">
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
+      </c>
+      <c r="AX4" s="17">
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
+      </c>
+      <c r="AY4" s="17">
+        <f t="shared" si="1"/>
+        <v>6.5621166063608434E-6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>172</v>
       </c>
       <c r="B5" s="17">
-        <f>efficiency!B5</f>
-        <v>5.2772702980209352E-5</v>
+        <f>efficiency!B5*'India cost adjustment'!$B$25</f>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="C5" s="17">
-        <f t="shared" si="1"/>
-        <v>5.2772702980209352E-5</v>
+        <f>$B5</f>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="D5" s="17">
         <f t="shared" si="1"/>
-        <v>5.2772702980209352E-5</v>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="E5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="F5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="G5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="H5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="I5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="J5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="K5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="L5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="M5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="N5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="O5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="P5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="Q5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="R5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="S5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="T5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="U5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="V5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="W5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="X5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="Y5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="Z5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="AA5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="AB5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="AC5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="AD5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="AE5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="AF5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="AG5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
       </c>
       <c r="AH5" s="17">
-        <f t="shared" si="0"/>
-        <v>5.2772702980209352E-5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
+      </c>
+      <c r="AI5" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
+      </c>
+      <c r="AJ5" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
+      </c>
+      <c r="AK5" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
+      </c>
+      <c r="AL5" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
+      </c>
+      <c r="AM5" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
+      </c>
+      <c r="AN5" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
+      </c>
+      <c r="AO5" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
+      </c>
+      <c r="AP5" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
+      </c>
+      <c r="AQ5" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
+      </c>
+      <c r="AR5" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
+      </c>
+      <c r="AS5" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
+      </c>
+      <c r="AT5" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
+      </c>
+      <c r="AU5" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
+      </c>
+      <c r="AV5" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
+      </c>
+      <c r="AW5" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
+      </c>
+      <c r="AX5" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
+      </c>
+      <c r="AY5" s="17">
+        <f t="shared" si="1"/>
+        <v>1.4373942225173853E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B6" s="17">
-        <f>'shift to electricity'!A53</f>
-        <v>4.604988339008401E-6</v>
+        <f>'shift to electricity'!A53*'India cost adjustment'!$B$25</f>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="C6" s="17">
-        <f t="shared" si="1"/>
-        <v>4.604988339008401E-6</v>
+        <f>$B6</f>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="D6" s="17">
         <f t="shared" si="1"/>
-        <v>4.604988339008401E-6</v>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="E6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="F6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="G6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="H6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="I6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="J6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="K6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="L6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="M6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="N6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="O6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="P6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="Q6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="R6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="S6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="T6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="U6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="V6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="W6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="X6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="Y6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="Z6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="AA6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="AB6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="AC6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="AD6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="AE6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="AF6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="AG6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
       </c>
       <c r="AH6" s="17">
-        <f t="shared" si="0"/>
-        <v>4.604988339008401E-6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
+      </c>
+      <c r="AI6" s="17">
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
+      </c>
+      <c r="AJ6" s="17">
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
+      </c>
+      <c r="AK6" s="17">
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
+      </c>
+      <c r="AL6" s="17">
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
+      </c>
+      <c r="AM6" s="17">
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
+      </c>
+      <c r="AN6" s="17">
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
+      </c>
+      <c r="AO6" s="17">
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
+      </c>
+      <c r="AP6" s="17">
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
+      </c>
+      <c r="AQ6" s="17">
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
+      </c>
+      <c r="AR6" s="17">
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
+      </c>
+      <c r="AS6" s="17">
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
+      </c>
+      <c r="AT6" s="17">
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
+      </c>
+      <c r="AU6" s="17">
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
+      </c>
+      <c r="AV6" s="17">
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
+      </c>
+      <c r="AW6" s="17">
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
+      </c>
+      <c r="AX6" s="17">
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
+      </c>
+      <c r="AY6" s="17">
+        <f t="shared" si="1"/>
+        <v>1.2542817137361547E-6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B7" s="17">
         <f>'shift to hydrogen'!A24</f>
         <v>6.1910177201439334E-6</v>
       </c>
       <c r="C7" s="17">
-        <f t="shared" si="1"/>
+        <f>$B7</f>
         <v>6.1910177201439334E-6</v>
       </c>
       <c r="D7" s="17">
@@ -3839,203 +4320,290 @@
         <v>6.1910177201439334E-6</v>
       </c>
       <c r="S7" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.1910177201439334E-6</v>
       </c>
       <c r="T7" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.1910177201439334E-6</v>
       </c>
       <c r="U7" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.1910177201439334E-6</v>
       </c>
       <c r="V7" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.1910177201439334E-6</v>
       </c>
       <c r="W7" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.1910177201439334E-6</v>
       </c>
       <c r="X7" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.1910177201439334E-6</v>
       </c>
       <c r="Y7" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.1910177201439334E-6</v>
       </c>
       <c r="Z7" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.1910177201439334E-6</v>
       </c>
       <c r="AA7" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.1910177201439334E-6</v>
       </c>
       <c r="AB7" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.1910177201439334E-6</v>
       </c>
       <c r="AC7" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.1910177201439334E-6</v>
       </c>
       <c r="AD7" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.1910177201439334E-6</v>
       </c>
       <c r="AE7" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.1910177201439334E-6</v>
       </c>
       <c r="AF7" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.1910177201439334E-6</v>
       </c>
       <c r="AG7" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>6.1910177201439334E-6</v>
       </c>
       <c r="AH7" s="17">
-        <f t="shared" si="0"/>
-        <v>6.1910177201439334E-6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AI7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AJ7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AK7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AL7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AM7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AN7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AO7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AP7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AQ7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AR7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AS7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AT7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AU7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AV7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AW7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AX7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+      <c r="AY7" s="17">
+        <f t="shared" si="1"/>
+        <v>6.1910177201439334E-6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="52">
+        <v>175</v>
+      </c>
+      <c r="B8">
         <v>0</v>
       </c>
       <c r="C8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="D8">
-        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="F8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="I8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="R8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="T8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="U8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="V8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="W8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="X8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Z8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AA8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AB8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AD8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AF8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AG8">
-        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AH8">
-        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
         <v>0</v>
       </c>
     </row>
@@ -4043,4 +4611,179 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{836E5932-0BA5-4E4B-8FC8-2417A875F708}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA5ACD59-1404-4FC7-8443-66AB8E715074}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A12DB4BE-784C-48F8-BBCE-641ADDA95B62}"/>
 </file>